--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95887</v>
+        <v>95892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95892</v>
+        <v>95895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95895</v>
+        <v>95905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95905</v>
+        <v>95912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95912</v>
+        <v>95914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95914</v>
+        <v>95940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95942</v>
+        <v>95946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50471-2024 artfynd.xlsx
+++ b/artfynd/A 50471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
